--- a/Tools/Config/Datas/AbilitySetting.xlsx
+++ b/Tools/Config/Datas/AbilitySetting.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ACTGameEditor\Tools\Config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6880"/>
+    <workbookView windowWidth="18350" windowHeight="6880" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="主动技能" sheetId="1" r:id="rId1"/>
     <sheet name="被动技能" sheetId="2" r:id="rId2"/>
-    <sheet name="主动技能伤害倍率" sheetId="4" r:id="rId3"/>
+    <sheet name="主动技能伤害倍率" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,20 +43,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 从10000开始
 </t>
         </r>
@@ -61,20 +57,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 ActiveSkill是主动
 PassiveSkill是被动
 </t>
@@ -85,20 +72,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 1为自身
 2为己方
 3为敌方</t>
@@ -109,20 +87,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 1为手动指定
 2为碰撞检测
 3为条件指定</t>
@@ -133,20 +102,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -157,20 +117,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -181,20 +132,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -205,20 +147,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -229,20 +162,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -253,20 +177,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -277,20 +192,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -301,20 +207,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -335,20 +232,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 从10000开始
 </t>
         </r>
@@ -358,20 +246,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 ActiveSkill是主动
 PassiveSkill是被动
 </t>
@@ -382,20 +261,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 1为自身
 2为己方
 3为敌方</t>
@@ -406,20 +276,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 1为手动指定
 2为碰撞检测
 3为条件指定</t>
@@ -430,20 +291,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -464,20 +316,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 从10000开始
 </t>
         </r>
@@ -487,20 +330,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 ActiveSkill是主动
 PassiveSkill是被动
 </t>
@@ -511,20 +345,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 1为自身
 2为己方
 3为敌方</t>
@@ -535,20 +360,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 #号分割
 第一个是方法名
 后面的均为参数</t>
@@ -560,7 +376,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -695,6 +511,24 @@
   </si>
   <si>
     <t>普攻3</t>
+  </si>
+  <si>
+    <t>时空断裂闪避</t>
+  </si>
+  <si>
+    <t>攻击后加攻</t>
+  </si>
+  <si>
+    <t>PassiveSkill</t>
+  </si>
+  <si>
+    <t>释放普攻或大招后 5 秒内攻击力提升 20%，重复攻击刷新时间</t>
+  </si>
+  <si>
+    <t>命中点燃</t>
+  </si>
+  <si>
+    <t>主动技能攻击命中后给敌人施加点燃</t>
   </si>
   <si>
     <t>SkillName</t>
@@ -759,7 +593,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -969,13 +803,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1458,48 +1286,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="22" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="23" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1811,366 +1639,372 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="16.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="17.4545454545455" customWidth="1"/>
-    <col min="5" max="5" width="20.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="20.3636363636364" customWidth="1"/>
-    <col min="7" max="7" width="17.3636363636364" customWidth="1"/>
-    <col min="8" max="8" width="19.4545454545455" customWidth="1"/>
-    <col min="9" max="9" width="28.4545454545455" customWidth="1"/>
-    <col min="10" max="10" width="22.8181818181818" customWidth="1"/>
-    <col min="11" max="12" width="24.2727272727273" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="23" customWidth="1"/>
-    <col min="15" max="15" width="21.4545454545455" customWidth="1"/>
-    <col min="16" max="16" width="19.4545454545455" customWidth="1"/>
-    <col min="17" max="17" width="22.4545454545455" customWidth="1"/>
+    <col min="3" max="3" width="16.8181818181818" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.4545454545455" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.8181818181818" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.3636363636364" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.3636363636364" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.4545454545455" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28.4545454545455" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22.8181818181818" style="2" customWidth="1"/>
+    <col min="11" max="12" width="24.2727272727273" style="2" customWidth="1"/>
+    <col min="13" max="13" width="22" style="2" customWidth="1"/>
+    <col min="14" max="14" width="23" style="2" customWidth="1"/>
+    <col min="15" max="15" width="21.4545454545455" style="2" customWidth="1"/>
+    <col min="16" max="16" width="19.4545454545455" style="2" customWidth="1"/>
+    <col min="17" max="17" width="22.4545454545455" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="17" customFormat="1" spans="1:31">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="18" customFormat="1" spans="1:31">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="21"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21"/>
     </row>
-    <row r="2" s="18" customFormat="1" spans="1:31">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="19" customFormat="1" spans="1:31">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
     </row>
-    <row r="3" s="19" customFormat="1" spans="1:31">
-      <c r="A3" s="7" t="s">
+    <row r="3" s="20" customFormat="1" spans="1:31">
+      <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
     </row>
-    <row r="4" s="17" customFormat="1" spans="1:31">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="18" customFormat="1" spans="1:31">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="20"/>
-      <c r="AD4" s="20"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
     </row>
     <row r="5" spans="1:31">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:31">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9">
+      <c r="A6" s="13"/>
+      <c r="B6" s="10">
         <v>11000</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <v>1</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="10">
         <v>1</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <v>2</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:31">
-      <c r="A7" s="12"/>
-      <c r="B7" s="9">
+      <c r="A7" s="13"/>
+      <c r="B7" s="10">
         <v>11001</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>3</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="10">
         <v>2</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="10">
         <v>0</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="12"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:31">
-      <c r="A8" s="12"/>
-      <c r="B8" s="9">
+      <c r="A8" s="13"/>
+      <c r="B8" s="10">
         <v>11002</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <v>3</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="10">
         <v>2</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="10">
         <v>0</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="12"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" spans="1:31">
-      <c r="A9" s="12"/>
-      <c r="B9" s="9">
+      <c r="A9" s="13"/>
+      <c r="B9" s="10">
         <v>11003</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <v>3</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="10">
         <v>2</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="10">
         <v>0</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="12"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="B10">
+        <v>11004</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2197,131 +2031,249 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.3636363636364" customWidth="1"/>
-    <col min="5" max="5" width="17.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.3636363636364" customWidth="1"/>
-    <col min="8" max="8" width="21.6363636363636" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="3" max="3" width="14" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.3636363636364" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.6363636363636" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.3636363636364" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.6363636363636" style="2" customWidth="1"/>
+    <col min="9" max="9" width="33" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:17">
+      <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:17">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="13" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="B6">
+        <v>19001</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="B7">
+        <v>19002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2343,191 +2295,191 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="3" max="3" width="16.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="13.2727272727273" customWidth="1"/>
-    <col min="5" max="5" width="19.7272727272727" customWidth="1"/>
-    <col min="6" max="6" width="20.3636363636364" customWidth="1"/>
-    <col min="7" max="7" width="17.6363636363636" customWidth="1"/>
-    <col min="8" max="8" width="25.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="16.8181818181818" customWidth="1"/>
-    <col min="10" max="10" width="15.3636363636364" customWidth="1"/>
-    <col min="11" max="11" width="14.2727272727273" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="3" max="3" width="16.4545454545455" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.2727272727273" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.7272727272727" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.3636363636364" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.6363636363636" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.2727272727273" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.8181818181818" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.3636363636364" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.2727272727273" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>50</v>
+      <c r="C1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>56</v>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13" spans="1:8">
-      <c r="A5" s="8" t="s">
+    <row r="5" s="1" customFormat="1" ht="13" customHeight="1" spans="1:8">
+      <c r="A5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>60</v>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9">
-        <v>11000</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9">
+      <c r="A6" s="13"/>
+      <c r="B6" s="10">
+        <v>11001</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10">
         <v>1</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <v>1</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="14">
+      <c r="F6" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="15">
         <v>0</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="12"/>
-      <c r="B7" s="9">
-        <v>11001</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9">
+      <c r="A7" s="13"/>
+      <c r="B7" s="10">
+        <v>11002</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10">
         <v>1</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>3</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="16">
+      <c r="F7" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="17">
         <v>0</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="12"/>
-      <c r="B8" s="9">
-        <v>11002</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9">
+      <c r="A8" s="13"/>
+      <c r="B8" s="10">
+        <v>11003</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10">
         <v>1</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <v>3</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="16">
+      <c r="F8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="17">
         <v>0</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="16">
         <v>1</v>
       </c>
     </row>

--- a/Tools/Config/Datas/AbilitySetting.xlsx
+++ b/Tools/Config/Datas/AbilitySetting.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6880" activeTab="2"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="主动技能" sheetId="1" r:id="rId1"/>
@@ -376,7 +376,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -429,6 +429,12 @@
     <t>CostB</t>
   </si>
   <si>
+    <t>SkillGroupId</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -480,7 +486,10 @@
     <t>技能释放不能有的标签</t>
   </si>
   <si>
-    <t>技能效果列表</t>
+    <t>命中额外效果</t>
+  </si>
+  <si>
+    <t>内联Buff效果</t>
   </si>
   <si>
     <t>消耗公式</t>
@@ -489,13 +498,28 @@
     <t>消耗属性</t>
   </si>
   <si>
-    <t>公式的A部分</t>
-  </si>
-  <si>
-    <t>公式的B部分</t>
-  </si>
-  <si>
-    <t>格式：FunName#param1#param2...</t>
+    <t>公式A</t>
+  </si>
+  <si>
+    <t>公式B</t>
+  </si>
+  <si>
+    <t>升级组；0=自身一组</t>
+  </si>
+  <si>
+    <t>技能等级上限</t>
+  </si>
+  <si>
+    <t>公式：FunName#param1#param2...</t>
+  </si>
+  <si>
+    <t>不要挂 SkillHpDamage</t>
+  </si>
+  <si>
+    <t>连招多 SkillId 填同一组</t>
+  </si>
+  <si>
+    <t>缺省 10</t>
   </si>
   <si>
     <t>翻滚闪避</t>
@@ -537,7 +561,7 @@
     <t>SegmentIndex</t>
   </si>
   <si>
-    <t>Ratio</t>
+    <t>RatioByLevel</t>
   </si>
   <si>
     <t>DamageType</t>
@@ -549,13 +573,19 @@
     <t>CanCrit</t>
   </si>
   <si>
+    <t>OnHitEffectIds</t>
+  </si>
+  <si>
+    <t>(list#sep=|),float</t>
+  </si>
+  <si>
     <t>技能名称</t>
   </si>
   <si>
-    <t>伤害段数</t>
-  </si>
-  <si>
-    <t>伤害系数</t>
+    <t>伤害段号</t>
+  </si>
+  <si>
+    <t>各级伤害系数</t>
   </si>
   <si>
     <t>伤害类型</t>
@@ -567,19 +597,43 @@
     <t>是否支持暴击</t>
   </si>
   <si>
-    <t>乘于当前攻击力</t>
-  </si>
-  <si>
-    <t>物冰火电</t>
+    <t>本段额外效果</t>
+  </si>
+  <si>
+    <t>从 1 开始</t>
+  </si>
+  <si>
+    <t>下标=等级-1；短了用最后一档</t>
+  </si>
+  <si>
+    <t>枚举值</t>
   </si>
   <si>
     <t>0为默认</t>
   </si>
   <si>
-    <t>0为不支持，1为支持</t>
+    <t>0不支持，1支持</t>
+  </si>
+  <si>
+    <t>空=无</t>
+  </si>
+  <si>
+    <t>1|1.1|1.2|1.3|1.4|1.5|1.6|1.7|1.8|1.9</t>
   </si>
   <si>
     <t>Physic</t>
+  </si>
+  <si>
+    <t>普攻2-1</t>
+  </si>
+  <si>
+    <t>1.5|1.65|1.8|1.95|2.1|2.25|2.4|2.55|2.7|2.85</t>
+  </si>
+  <si>
+    <t>普攻2-2</t>
+  </si>
+  <si>
+    <t>3|3.3|3.6|3.9|4.2|4.5|4.8|5.1|5.4|5.7</t>
   </si>
 </sst>
 </file>
@@ -1710,8 +1764,12 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
+      <c r="R1" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>18</v>
+      </c>
       <c r="T1" s="21"/>
       <c r="U1" s="21"/>
       <c r="V1" s="21"/>
@@ -1748,58 +1806,62 @@
     </row>
     <row r="3" s="20" customFormat="1" spans="1:31">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="O3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="4" t="s">
+      <c r="R3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="S3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
       <c r="T3" s="21"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
@@ -1815,58 +1877,62 @@
     </row>
     <row r="4" s="18" customFormat="1" spans="1:31">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
+        <v>41</v>
+      </c>
+      <c r="R4" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" s="21" t="s">
+        <v>43</v>
+      </c>
       <c r="T4" s="21"/>
       <c r="U4" s="21"/>
       <c r="V4" s="21"/>
@@ -1881,7 +1947,7 @@
     </row>
     <row r="5" spans="1:31">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -1891,7 +1957,16 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="13" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -1900,10 +1975,10 @@
         <v>11000</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E6" s="10">
         <v>1</v>
@@ -1916,6 +1991,12 @@
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="13"/>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:31">
       <c r="A7" s="13"/>
@@ -1923,10 +2004,10 @@
         <v>11001</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E7" s="10">
         <v>3</v>
@@ -1939,6 +2020,12 @@
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
+      <c r="R7">
+        <v>11001</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:31">
       <c r="A8" s="13"/>
@@ -1946,10 +2033,10 @@
         <v>11002</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E8" s="10">
         <v>3</v>
@@ -1962,6 +2049,12 @@
       </c>
       <c r="H8" s="10"/>
       <c r="I8" s="13"/>
+      <c r="R8">
+        <v>11001</v>
+      </c>
+      <c r="S8">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:31">
       <c r="A9" s="13"/>
@@ -1969,10 +2062,10 @@
         <v>11003</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E9" s="10">
         <v>3</v>
@@ -1985,16 +2078,22 @@
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="13"/>
+      <c r="R9">
+        <v>11001</v>
+      </c>
+      <c r="S9">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:31">
       <c r="B10">
         <v>11004</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2004,6 +2103,12 @@
       </c>
       <c r="G10">
         <v>2</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2031,7 +2136,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="3" max="3" width="14" style="2" customWidth="1"/>
@@ -2043,7 +2148,7 @@
     <col min="9" max="9" width="33" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2095,8 +2200,14 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2109,115 +2220,127 @@
       <c r="H2" s="7"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:19">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="s">
+      <c r="Q3" t="s">
         <v>22</v>
       </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:19">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2227,18 +2350,27 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="13" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>19001</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2250,18 +2382,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>56</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>19002</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -2273,7 +2411,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>58</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2292,12 +2436,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="16.4545454545455" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.2727272727273" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.7272727272727" style="2" customWidth="1"/>
+    <col min="5" max="5" width="47.5454545454545" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.3636363636364" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.6363636363636" style="2" customWidth="1"/>
     <col min="8" max="8" width="25.2727272727273" style="2" customWidth="1"/>
@@ -2307,7 +2451,7 @@
     <col min="12" max="12" width="19" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2315,25 +2459,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2345,92 +2492,105 @@
       <c r="G2" s="7"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
+      </c>
+      <c r="I4" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13" customHeight="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="13" customHeight="1" spans="1:9">
       <c r="A5" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="E5" s="11" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>66</v>
+        <v>78</v>
+      </c>
+      <c r="I5" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="13"/>
       <c r="B6" s="10">
         <v>11001</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D6" s="10">
         <v>1</v>
       </c>
-      <c r="E6" s="14">
-        <v>1</v>
+      <c r="E6" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G6" s="15">
         <v>0</v>
@@ -2439,20 +2599,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="13"/>
       <c r="B7" s="10">
         <v>11002</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="D7" s="10">
         <v>1</v>
       </c>
-      <c r="E7" s="14">
-        <v>3</v>
+      <c r="E7" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G7" s="17">
         <v>0</v>
@@ -2461,25 +2623,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="13"/>
       <c r="B8" s="10">
-        <v>11003</v>
-      </c>
-      <c r="C8" s="10"/>
+        <v>11002</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>84</v>
+      </c>
       <c r="D8" s="10">
-        <v>1</v>
-      </c>
-      <c r="E8" s="14">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G8" s="17">
         <v>0</v>
       </c>
       <c r="H8" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9">
+        <v>11003</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
     </row>

--- a/Tools/Config/Datas/AbilitySetting.xlsx
+++ b/Tools/Config/Datas/AbilitySetting.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18350" windowHeight="6880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18350" windowHeight="6880" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="主动技能" sheetId="1" state="visible" r:id="rId1"/>
@@ -725,6 +725,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="23"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="22"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -755,7 +756,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1331,7 +1331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16.8181818181818" customWidth="1" style="2" min="3" max="3"/>
@@ -1350,7 +1350,7 @@
     <col width="22.4545454545455" customWidth="1" style="2" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="18">
+    <row r="1" customFormat="1" s="19">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>##var</t>
@@ -1436,30 +1436,30 @@
           <t>CostB</t>
         </is>
       </c>
-      <c r="R1" s="21" t="inlineStr">
+      <c r="R1" s="22" t="inlineStr">
         <is>
           <t>SkillGroupId</t>
         </is>
       </c>
-      <c r="S1" s="21" t="inlineStr">
+      <c r="S1" s="22" t="inlineStr">
         <is>
           <t>MaxLevel</t>
         </is>
       </c>
-      <c r="T1" s="21" t="n"/>
-      <c r="U1" s="21" t="n"/>
-      <c r="V1" s="21" t="n"/>
-      <c r="W1" s="21" t="n"/>
-      <c r="X1" s="21" t="n"/>
-      <c r="Y1" s="21" t="n"/>
-      <c r="Z1" s="21" t="n"/>
-      <c r="AA1" s="21" t="n"/>
-      <c r="AB1" s="21" t="n"/>
-      <c r="AC1" s="21" t="n"/>
-      <c r="AD1" s="21" t="n"/>
-      <c r="AE1" s="21" t="n"/>
-    </row>
-    <row r="2" customFormat="1" s="19">
+      <c r="T1" s="22" t="n"/>
+      <c r="U1" s="22" t="n"/>
+      <c r="V1" s="22" t="n"/>
+      <c r="W1" s="22" t="n"/>
+      <c r="X1" s="22" t="n"/>
+      <c r="Y1" s="22" t="n"/>
+      <c r="Z1" s="22" t="n"/>
+      <c r="AA1" s="22" t="n"/>
+      <c r="AB1" s="22" t="n"/>
+      <c r="AC1" s="22" t="n"/>
+      <c r="AD1" s="22" t="n"/>
+      <c r="AE1" s="22" t="n"/>
+    </row>
+    <row r="2" customFormat="1" s="20">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>##var</t>
@@ -1482,8 +1482,8 @@
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n"/>
     </row>
-    <row r="3" customFormat="1" s="20">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" customFormat="1" s="21">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
@@ -1568,30 +1568,30 @@
           <t>float</t>
         </is>
       </c>
-      <c r="R3" s="21" t="inlineStr">
+      <c r="R3" s="22" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="S3" s="21" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T3" s="21" t="n"/>
-      <c r="U3" s="21" t="n"/>
-      <c r="V3" s="21" t="n"/>
-      <c r="W3" s="21" t="n"/>
-      <c r="X3" s="21" t="n"/>
-      <c r="Y3" s="21" t="n"/>
-      <c r="Z3" s="21" t="n"/>
-      <c r="AA3" s="21" t="n"/>
-      <c r="AB3" s="21" t="n"/>
-      <c r="AC3" s="21" t="n"/>
-      <c r="AD3" s="21" t="n"/>
-      <c r="AE3" s="21" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="18">
+      <c r="T3" s="22" t="n"/>
+      <c r="U3" s="22" t="n"/>
+      <c r="V3" s="22" t="n"/>
+      <c r="W3" s="22" t="n"/>
+      <c r="X3" s="22" t="n"/>
+      <c r="Y3" s="22" t="n"/>
+      <c r="Z3" s="22" t="n"/>
+      <c r="AA3" s="22" t="n"/>
+      <c r="AB3" s="22" t="n"/>
+      <c r="AC3" s="22" t="n"/>
+      <c r="AD3" s="22" t="n"/>
+      <c r="AE3" s="22" t="n"/>
+    </row>
+    <row r="4" customFormat="1" s="19">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>##</t>
@@ -1677,27 +1677,27 @@
           <t>公式B</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>升级组；0=自身一组</t>
         </is>
       </c>
-      <c r="S4" s="21" t="inlineStr">
+      <c r="S4" s="22" t="inlineStr">
         <is>
           <t>技能等级上限</t>
         </is>
       </c>
-      <c r="T4" s="21" t="n"/>
-      <c r="U4" s="21" t="n"/>
-      <c r="V4" s="21" t="n"/>
-      <c r="W4" s="21" t="n"/>
-      <c r="X4" s="21" t="n"/>
-      <c r="Y4" s="21" t="n"/>
-      <c r="Z4" s="21" t="n"/>
-      <c r="AA4" s="21" t="n"/>
-      <c r="AB4" s="21" t="n"/>
-      <c r="AC4" s="21" t="n"/>
-      <c r="AD4" s="21" t="n"/>
+      <c r="T4" s="22" t="n"/>
+      <c r="U4" s="22" t="n"/>
+      <c r="V4" s="22" t="n"/>
+      <c r="W4" s="22" t="n"/>
+      <c r="X4" s="22" t="n"/>
+      <c r="Y4" s="22" t="n"/>
+      <c r="Z4" s="22" t="n"/>
+      <c r="AA4" s="22" t="n"/>
+      <c r="AB4" s="22" t="n"/>
+      <c r="AC4" s="22" t="n"/>
+      <c r="AD4" s="22" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1705,14 +1705,14 @@
           <t>##</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>公式：FunName#param1#param2...</t>
         </is>
@@ -1734,31 +1734,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n"/>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="11" t="n">
         <v>11000</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>翻滚闪避</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>ActiveSkill</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="14" t="n"/>
       <c r="R6" s="0" t="n">
         <v>0</v>
       </c>
@@ -1767,31 +1767,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n"/>
-      <c r="B7" s="10" t="n">
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="11" t="n">
         <v>11001</v>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>普攻1</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>ActiveSkill</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="13" t="n"/>
+      <c r="G7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="14" t="n"/>
       <c r="R7" s="0" t="n">
         <v>11001</v>
       </c>
@@ -1800,31 +1800,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="11" t="n">
         <v>11002</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>普攻2</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>ActiveSkill</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="13" t="n"/>
+      <c r="G8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="14" t="n"/>
       <c r="R8" s="0" t="n">
         <v>11001</v>
       </c>
@@ -1833,31 +1833,31 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="10" t="n">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="11" t="n">
         <v>11003</v>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>普攻3</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>ActiveSkill</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="13" t="n"/>
+      <c r="G9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="14" t="n"/>
       <c r="R9" s="0" t="n">
         <v>11001</v>
       </c>
@@ -1896,28 +1896,31 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="0" t="n">
-        <v>12001</v>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>敌普攻1</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="11" t="n">
+        <v>11005</v>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>招架</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>ActiveSkill</t>
         </is>
       </c>
-      <c r="E11" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="0" t="n">
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="14" t="n"/>
       <c r="R11" s="0" t="n">
         <v>0</v>
       </c>
@@ -1927,11 +1930,11 @@
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
-        <v>12002</v>
+        <v>12001</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>敌普攻2</t>
+          <t>敌普攻1</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -1957,11 +1960,11 @@
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>敌普攻3</t>
+          <t>敌普攻2</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -1987,11 +1990,11 @@
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
-        <v>12004</v>
+        <v>12003</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>敌红光重击</t>
+          <t>敌普攻3</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -2017,11 +2020,11 @@
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
-        <v>12005</v>
+        <v>12004</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>敌虚招(假前摇)</t>
+          <t>敌红光重击</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -2042,6 +2045,96 @@
         <v>0</v>
       </c>
       <c r="S15" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="n">
+        <v>12005</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>敌虚招(假前摇)</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>ActiveSkill</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="n">
+        <v>12006</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>敌黄闪近劈</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>ActiveSkill</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>连携技</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>ActiveSkill</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="0" t="n">
+        <v>13001</v>
+      </c>
+      <c r="S18" s="0" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2197,7 +2290,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
@@ -2396,14 +2489,14 @@
           <t>##</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>公式：FunName#param1#param2...</t>
         </is>
@@ -2512,7 +2605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col width="16.4545454545455" customWidth="1" style="2" min="3" max="3"/>
@@ -2583,6 +2676,11 @@
           <t>OnHitEffectIds</t>
         </is>
       </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>DazeRatio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2597,10 +2695,11 @@
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="3" t="n"/>
-      <c r="I2" s="22" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
@@ -2653,6 +2752,11 @@
       <c r="K3" s="0" t="inlineStr">
         <is>
           <t>(list#sep=|),int</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
@@ -2712,41 +2816,46 @@
           <t>本段额外效果</t>
         </is>
       </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>失衡倍率</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13" customFormat="1" customHeight="1" s="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>从 1 开始</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>下标=等级-1；短了用最后一档</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>枚举值</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>0为默认</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>0不支持，1支持</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Light轻受击 / Heavy重受击；空=Light</t>
         </is>
@@ -2761,18 +2870,23 @@
           <t>空=无</t>
         </is>
       </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>0=不贡献。积蓄=100*本值*(1-抗性)。杂兵上限100时 0.55=两下11001满</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n"/>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="11" t="n">
         <v>11001</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>普攻1</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -2780,18 +2894,18 @@
           <t>1|1.1|1.2|1.3|1.4|1.5|1.6|1.7|1.8|1.9</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="16" t="n">
+      <c r="G6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
@@ -2799,18 +2913,21 @@
       <c r="J6" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="0" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n"/>
-      <c r="B7" s="10" t="n">
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="11" t="n">
         <v>11002</v>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>普攻2-1</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -2818,18 +2935,18 @@
           <t>1.5|1.65|1.8|1.95|2.1|2.25|2.4|2.55|2.7|2.85</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="16" t="n">
+      <c r="G7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
@@ -2837,18 +2954,21 @@
       <c r="J7" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="L7" s="0" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
-      <c r="B8" s="10" t="n">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="11" t="n">
         <v>11002</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>普攻2-2</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -2856,24 +2976,27 @@
           <t>1.5|1.65|1.8|1.95|2.1|2.25|2.4|2.55|2.7|2.85</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="16" t="n">
+      <c r="G8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
       <c r="J8" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="9">
@@ -2912,6 +3035,9 @@
       <c r="J9" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="L9" s="0" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="n">
@@ -2949,14 +3075,17 @@
       <c r="J10" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="L10" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="n">
-        <v>12002</v>
+        <v>12006</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>敌普攻2-1</t>
+          <t>敌黄闪近劈</t>
         </is>
       </c>
       <c r="D11" s="0" t="n">
@@ -2964,7 +3093,7 @@
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>1.5|1.65|1.8|1.95|2.1|2.25|2.4|2.55|2.7|2.85</t>
+          <t>1|1.1|1.2|1.3|1.4|1.5|1.6|1.7|1.8|1.9</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -2984,6 +3113,9 @@
         </is>
       </c>
       <c r="J11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2993,11 +3125,11 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>敌普攻2-2</t>
+          <t>敌普攻2-1</t>
         </is>
       </c>
       <c r="D12" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -3017,28 +3149,31 @@
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="J12" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>敌普攻3</t>
+          <t>敌普攻2-2</t>
         </is>
       </c>
       <c r="D13" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>3|3.3|3.6|3.9|4.2|4.5|4.8|5.1|5.4|5.7</t>
+          <t>1.5|1.65|1.8|1.95|2.1|2.25|2.4|2.55|2.7|2.85</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -3060,14 +3195,17 @@
       <c r="J13" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="L13" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
-        <v>12004</v>
+        <v>12003</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>敌红光重击</t>
+          <t>敌普攻3</t>
         </is>
       </c>
       <c r="D14" s="0" t="n">
@@ -3075,7 +3213,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>4|4.4|4.8|5.2|5.6|6|6.4|6.8|7.2|7.6</t>
+          <t>3|3.3|3.6|3.9|4.2|4.5|4.8|5.1|5.4|5.7</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -3095,7 +3233,250 @@
         </is>
       </c>
       <c r="J14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="n">
+        <v>12004</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>敌红光重击</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>4|4.4|4.8|5.2|5.6|6|6.4|6.8|7.2|7.6</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Physic</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
         <v>5</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="2">
+      <c r="B16" s="0" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>连携技</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Physic</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="2">
+      <c r="B17" s="0" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>连携技</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Physic</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="2">
+      <c r="B18" s="0" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>连携技</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Physic</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="2">
+      <c r="B19" s="0" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>连携技</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Physic</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>连携技</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Physic</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
